--- a/base_datas/crescimento_medio_receita_uf.xlsx
+++ b/base_datas/crescimento_medio_receita_uf.xlsx
@@ -373,7 +373,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>275.4025553363841</v>
+        <v>352.8258985015473</v>
       </c>
     </row>
     <row r="3">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>500.5161576068715</v>
+        <v>518.3684480205009</v>
       </c>
     </row>
     <row r="4">
@@ -393,7 +393,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>456.4609447365203</v>
+        <v>506.8549843108698</v>
       </c>
     </row>
     <row r="5">
@@ -403,7 +403,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>388.3520559570472</v>
+        <v>438.5692685942599</v>
       </c>
     </row>
     <row r="6">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>343.1146435057699</v>
+        <v>370.2936554964252</v>
       </c>
     </row>
     <row r="7">
@@ -423,7 +423,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>366.2668457124603</v>
+        <v>402.6280030220175</v>
       </c>
     </row>
     <row r="8">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>18.05141344379977</v>
+        <v>21.3795006176337</v>
       </c>
     </row>
     <row r="9">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>288.2147456895664</v>
+        <v>312.0432099511598</v>
       </c>
     </row>
     <row r="10">
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>298.0203047900593</v>
+        <v>331.8499491667074</v>
       </c>
     </row>
     <row r="11">
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>464.6281966627985</v>
+        <v>508.1568039835303</v>
       </c>
     </row>
     <row r="12">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>295.0623179330288</v>
+        <v>323.1941554943357</v>
       </c>
     </row>
     <row r="13">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>324.1993797114977</v>
+        <v>342.185832724832</v>
       </c>
     </row>
     <row r="14">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>327.2706132459926</v>
+        <v>365.4276025590669</v>
       </c>
     </row>
     <row r="15">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>422.4501355503825</v>
+        <v>460.1905992548718</v>
       </c>
     </row>
     <row r="16">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>345.3110179568606</v>
+        <v>373.4769569342349</v>
       </c>
     </row>
     <row r="17">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>353.5692168458702</v>
+        <v>377.6397664734981</v>
       </c>
     </row>
     <row r="18">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>528.0477401556266</v>
+        <v>586.1325603769413</v>
       </c>
     </row>
     <row r="19">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>284.2719903905407</v>
+        <v>314.1387770933393</v>
       </c>
     </row>
     <row r="20">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>258.6809713940111</v>
+        <v>278.744094945122</v>
       </c>
     </row>
     <row r="21">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>324.0509449514581</v>
+        <v>356.2342620515776</v>
       </c>
     </row>
     <row r="22">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>383.8055136001887</v>
+        <v>434.4008070131296</v>
       </c>
     </row>
     <row r="23">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>505.9266376837874</v>
+        <v>574.5377243814069</v>
       </c>
     </row>
     <row r="24">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>271.2047503273172</v>
+        <v>288.4352373823964</v>
       </c>
     </row>
     <row r="25">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>291.5635850904328</v>
+        <v>311.5186906083576</v>
       </c>
     </row>
     <row r="26">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>334.0605914144251</v>
+        <v>359.2509945671575</v>
       </c>
     </row>
     <row r="27">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>183.0302869719002</v>
+        <v>194.8915461529145</v>
       </c>
     </row>
     <row r="28">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>423.4490678642364</v>
+        <v>439.4367198199809</v>
       </c>
     </row>
   </sheetData>
